--- a/data-manipulation-scripts/sheets-cleanup/sheets/FILTRO OLEO NOVO 18_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/FILTRO OLEO NOVO 18_02.xlsx
@@ -366,7 +366,9 @@
       <c r="C3" s="2">
         <v>10.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -375,8 +377,12 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
